--- a/sektorler/İnşaat- Taahhüt.xlsx
+++ b/sektorler/İnşaat- Taahhüt.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,177 +417,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ana Ortaklığa Ait Özkaynaklar</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ödenmiş Sermaye</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net_borc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>duzeltilmis_fiyat</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Satış Gelirleri</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net Faaliyet Kar/Zararı</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FAVÖK</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ana Ortaklık Payları</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>F/K</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FD/FAVÖK</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FD/NS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>PD/DD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>NFK/PD_%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Sektör</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>F/K (PD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>FD/FAVÖK (PD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FD/NS (PD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>PD/DD (PD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin PD</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin Fiyat</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>iskonto_%</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>YEOTK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4128563110</v>
+        <v>4550322502</v>
       </c>
       <c r="C2" t="n">
         <v>355000000</v>
       </c>
       <c r="D2" t="n">
-        <v>5156106872</v>
+        <v>6689384143</v>
       </c>
       <c r="E2" t="n">
-        <v>55.09999847412109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F2" t="n">
-        <v>19560499458.31299</v>
+        <v>38659500541.68701</v>
       </c>
       <c r="G2" t="n">
-        <v>24716606330.31299</v>
+        <v>45348884684.68701</v>
       </c>
       <c r="H2" t="n">
-        <v>16733157490</v>
+        <v>20338868404</v>
       </c>
       <c r="I2" t="n">
-        <v>2997982496</v>
+        <v>4331518773</v>
       </c>
       <c r="J2" t="n">
-        <v>3176819029</v>
+        <v>4548935001</v>
       </c>
       <c r="K2" t="n">
-        <v>1477665556</v>
+        <v>1754933090</v>
       </c>
       <c r="L2" t="n">
-        <v>13.23743344959784</v>
+        <v>22.02904530205594</v>
       </c>
       <c r="M2" t="n">
-        <v>7.780300390007827</v>
+        <v>9.969121272279752</v>
       </c>
       <c r="N2" t="n">
-        <v>1.477103549947703</v>
+        <v>2.22966606518622</v>
       </c>
       <c r="O2" t="n">
-        <v>4.737846785225233</v>
+        <v>8.495991333514279</v>
       </c>
       <c r="P2" t="n">
-        <v>15.32671751245029</v>
+        <v>11.20428022169937</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -607,77 +595,77 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>34033761914.17074</v>
+        <v>34247642040.67016</v>
       </c>
       <c r="S2" t="n">
-        <v>43244790087.03706</v>
+        <v>50078909020.1935</v>
       </c>
       <c r="T2" t="n">
-        <v>33971378333.13626</v>
+        <v>33633999317.88495</v>
       </c>
       <c r="U2" t="n">
-        <v>7493621491.460883</v>
+        <v>7262277827.460985</v>
       </c>
       <c r="V2" t="n">
-        <v>29685887956.45124</v>
+        <v>31305707051.5524</v>
       </c>
       <c r="W2" t="n">
-        <v>83.62221959563729</v>
+        <v>88.1850902860631</v>
       </c>
       <c r="X2" t="n">
-        <v>-34.1084238847497</v>
+        <v>23.4902648198452</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GLRMK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17746392856</v>
+        <v>18936263841</v>
       </c>
       <c r="C3" t="n">
         <v>322600000</v>
       </c>
       <c r="D3" t="n">
-        <v>-686349263</v>
+        <v>2319432829</v>
       </c>
       <c r="E3" t="n">
-        <v>192</v>
+        <v>170.8999938964844</v>
       </c>
       <c r="F3" t="n">
-        <v>61939200000</v>
+        <v>55132338031.00586</v>
       </c>
       <c r="G3" t="n">
-        <v>61252850737</v>
+        <v>57451770860.00586</v>
       </c>
       <c r="H3" t="n">
-        <v>45532849493</v>
+        <v>50817559234</v>
       </c>
       <c r="I3" t="n">
-        <v>4937231669</v>
+        <v>5425303515</v>
       </c>
       <c r="J3" t="n">
-        <v>6099126336</v>
+        <v>6723378727</v>
       </c>
       <c r="K3" t="n">
-        <v>4279432663</v>
+        <v>3793333361</v>
       </c>
       <c r="L3" t="n">
-        <v>14.47369426688885</v>
+        <v>14.53400816227547</v>
       </c>
       <c r="M3" t="n">
-        <v>10.04288931932037</v>
+        <v>8.545074313497892</v>
       </c>
       <c r="N3" t="n">
-        <v>1.345245277179868</v>
+        <v>1.130549592030921</v>
       </c>
       <c r="O3" t="n">
-        <v>3.490241679117261</v>
+        <v>2.911468624113467</v>
       </c>
       <c r="P3" t="n">
-        <v>7.971093699950919</v>
+        <v>9.840510503923968</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -685,77 +673,77 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>98564382034.13579</v>
+        <v>74027165952.21317</v>
       </c>
       <c r="S3" t="n">
-        <v>93610492134.87439</v>
+        <v>81584763326.27821</v>
       </c>
       <c r="T3" t="n">
-        <v>107156744700.9057</v>
+        <v>98430318181.52415</v>
       </c>
       <c r="U3" t="n">
-        <v>32210904219.80481</v>
+        <v>30222123589.48212</v>
       </c>
       <c r="V3" t="n">
-        <v>82885630772.43018</v>
+        <v>71066092762.37442</v>
       </c>
       <c r="W3" t="n">
-        <v>256.930039592158</v>
+        <v>220.2916700631569</v>
       </c>
       <c r="X3" t="n">
-        <v>-25.27148623618545</v>
+        <v>-22.42103668854665</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ENKAI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373216949000</v>
+        <v>386633607000</v>
       </c>
       <c r="C4" t="n">
         <v>6021689000</v>
       </c>
       <c r="D4" t="n">
-        <v>-213270511000</v>
+        <v>-183822192000</v>
       </c>
       <c r="E4" t="n">
-        <v>106.3000030517578</v>
+        <v>93.30000305175781</v>
       </c>
       <c r="F4" t="n">
-        <v>640105559076.7365</v>
+        <v>561823602076.7365</v>
       </c>
       <c r="G4" t="n">
-        <v>426835048076.7365</v>
+        <v>378001410076.7365</v>
       </c>
       <c r="H4" t="n">
-        <v>156507106000</v>
+        <v>178183478033</v>
       </c>
       <c r="I4" t="n">
-        <v>28479859000</v>
+        <v>32399598810</v>
       </c>
       <c r="J4" t="n">
-        <v>33943633000</v>
+        <v>38913746922</v>
       </c>
       <c r="K4" t="n">
-        <v>36183302000</v>
+        <v>39366444461</v>
       </c>
       <c r="L4" t="n">
-        <v>17.69063417917846</v>
+        <v>14.27163691740894</v>
       </c>
       <c r="M4" t="n">
-        <v>12.57481920325784</v>
+        <v>9.713827117044652</v>
       </c>
       <c r="N4" t="n">
-        <v>2.727256665756355</v>
+        <v>2.121416723085457</v>
       </c>
       <c r="O4" t="n">
-        <v>1.715103134495471</v>
+        <v>1.453116314528593</v>
       </c>
       <c r="P4" t="n">
-        <v>4.44924412796512</v>
+        <v>5.766863245018089</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -763,77 +751,77 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>833377945730.8661</v>
+        <v>768238918051.4287</v>
       </c>
       <c r="S4" t="n">
-        <v>730423760288.3372</v>
+        <v>669445088977.1588</v>
       </c>
       <c r="T4" t="n">
-        <v>579234285510.1802</v>
+        <v>537084751568.2491</v>
       </c>
       <c r="U4" t="n">
-        <v>677414024077.704</v>
+        <v>617064102650.5784</v>
       </c>
       <c r="V4" t="n">
-        <v>705112503901.7719</v>
+        <v>647958215311.8538</v>
       </c>
       <c r="W4" t="n">
-        <v>117.0954700420051</v>
+        <v>107.6040651238969</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.219372010185111</v>
+        <v>-13.29323576731902</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>AKFIS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31682767000</v>
+        <v>35674236000</v>
       </c>
       <c r="C5" t="n">
         <v>636584000</v>
       </c>
       <c r="D5" t="n">
-        <v>19850136000</v>
+        <v>19383630000</v>
       </c>
       <c r="E5" t="n">
-        <v>52.09999847412109</v>
+        <v>64.80000305175781</v>
       </c>
       <c r="F5" t="n">
-        <v>33166025428.6499</v>
+        <v>41250645142.7002</v>
       </c>
       <c r="G5" t="n">
-        <v>53016161428.6499</v>
+        <v>60634275142.7002</v>
       </c>
       <c r="H5" t="n">
-        <v>9732579000</v>
+        <v>11188406323</v>
       </c>
       <c r="I5" t="n">
-        <v>231610000</v>
+        <v>466577034</v>
       </c>
       <c r="J5" t="n">
-        <v>290957000</v>
+        <v>526051573</v>
       </c>
       <c r="K5" t="n">
-        <v>1685694000</v>
+        <v>2811545517</v>
       </c>
       <c r="L5" t="n">
-        <v>19.67499761442463</v>
+        <v>14.67187527047964</v>
       </c>
       <c r="M5" t="n">
-        <v>182.2130466998557</v>
+        <v>115.2629860926206</v>
       </c>
       <c r="N5" t="n">
-        <v>5.447288065028797</v>
+        <v>5.419384440664651</v>
       </c>
       <c r="O5" t="n">
-        <v>1.046815937151256</v>
+        <v>1.156314746101366</v>
       </c>
       <c r="P5" t="n">
-        <v>0.698335109518211</v>
+        <v>1.131078150137893</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -841,75 +829,75 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>38825096804.3449</v>
+        <v>54867507482.73083</v>
       </c>
       <c r="S5" t="n">
-        <v>-15417217521.4981</v>
+        <v>-12818785721.40331</v>
       </c>
       <c r="T5" t="n">
-        <v>2907753003.190151</v>
+        <v>2798252960.105652</v>
       </c>
       <c r="U5" t="n">
-        <v>57506366591.5834</v>
+        <v>56935791474.23922</v>
       </c>
       <c r="V5" t="n">
-        <v>20955499719.40509</v>
+        <v>25445691548.9181</v>
       </c>
       <c r="W5" t="n">
-        <v>32.91867172188601</v>
+        <v>39.97224490235082</v>
       </c>
       <c r="X5" t="n">
-        <v>58.26883573641386</v>
+        <v>62.11249383180586</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>KUYAS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1433769960</v>
+        <v>1771741339</v>
       </c>
       <c r="C6" t="n">
         <v>400000000</v>
       </c>
       <c r="D6" t="n">
-        <v>663098337</v>
+        <v>450938593</v>
       </c>
       <c r="E6" t="n">
-        <v>91.19999694824219</v>
+        <v>72.80000305175781</v>
       </c>
       <c r="F6" t="n">
-        <v>36479998779.29688</v>
+        <v>29120001220.70312</v>
       </c>
       <c r="G6" t="n">
-        <v>37143097116.29688</v>
+        <v>29570939813.70312</v>
       </c>
       <c r="H6" t="n">
-        <v>1189922595</v>
+        <v>1131697251</v>
       </c>
       <c r="I6" t="n">
-        <v>99207715</v>
+        <v>90318512</v>
       </c>
       <c r="J6" t="n">
-        <v>106419739</v>
+        <v>95628372</v>
       </c>
       <c r="K6" t="n">
-        <v>-1311891342</v>
+        <v>-1561410104</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>349.0245086609062</v>
+        <v>309.2276820701614</v>
       </c>
       <c r="N6" t="n">
-        <v>31.21471705165568</v>
+        <v>26.12972664515479</v>
       </c>
       <c r="O6" t="n">
-        <v>25.44341128425991</v>
+        <v>16.43580842175243</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2719509822360585</v>
+        <v>0.3101597122729076</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -917,66 +905,66 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>-30215631277.04788</v>
+        <v>-30471027428.44604</v>
       </c>
       <c r="S6" t="n">
-        <v>958275362.5172784</v>
+        <v>742452707.4299982</v>
       </c>
       <c r="T6" t="n">
-        <v>2119322061.477935</v>
+        <v>1792738946.342732</v>
       </c>
       <c r="U6" t="n">
-        <v>2602389523.861974</v>
+        <v>2827684814.990667</v>
       </c>
       <c r="V6" t="n">
-        <v>-6133911082.297673</v>
+        <v>-6277037739.920663</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TKFEN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32385652000</v>
+        <v>35055157000</v>
       </c>
       <c r="C7" t="n">
         <v>370000000</v>
       </c>
       <c r="D7" t="n">
-        <v>6020591000</v>
+        <v>6210174000</v>
       </c>
       <c r="E7" t="n">
-        <v>141.3000030517578</v>
+        <v>139.3999938964844</v>
       </c>
       <c r="F7" t="n">
-        <v>52281001129.15039</v>
+        <v>51577997741.69922</v>
       </c>
       <c r="G7" t="n">
-        <v>58301592129.15039</v>
+        <v>57788171741.69922</v>
       </c>
       <c r="H7" t="n">
-        <v>53909396000</v>
+        <v>56318844153</v>
       </c>
       <c r="I7" t="n">
-        <v>-2797061000</v>
+        <v>-3251280635</v>
       </c>
       <c r="J7" t="n">
-        <v>-14292000</v>
+        <v>-211364941</v>
       </c>
       <c r="K7" t="n">
-        <v>-5721464000</v>
+        <v>-5871101622</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1.081473666096173</v>
+        <v>1.0260894485815</v>
       </c>
       <c r="O7" t="n">
-        <v>1.614326033304822</v>
+        <v>1.471338375169714</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
@@ -985,72 +973,70 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>-131777412544.9663</v>
+        <v>-114574958943.1093</v>
       </c>
       <c r="S7" t="n">
-        <v>-6238338883.346162</v>
+        <v>-8847896221.238899</v>
       </c>
       <c r="T7" t="n">
-        <v>120036854862.7074</v>
+        <v>105446300870.9722</v>
       </c>
       <c r="U7" t="n">
-        <v>58782150442.20873</v>
+        <v>55947746408.60472</v>
       </c>
       <c r="V7" t="n">
-        <v>10200813469.15092</v>
+        <v>9492798028.807182</v>
       </c>
       <c r="W7" t="n">
-        <v>27.56976613284032</v>
+        <v>25.65621088866806</v>
       </c>
       <c r="X7" t="n">
-        <v>412.5179603299039</v>
+        <v>443.3381979178193</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>YYAPI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5215539183</v>
+        <v>5623639508</v>
       </c>
       <c r="C8" t="n">
         <v>1705025558</v>
       </c>
       <c r="D8" t="n">
-        <v>-29942721</v>
+        <v>-30323106</v>
       </c>
       <c r="E8" t="n">
-        <v>1.139999985694885</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="F8" t="n">
-        <v>1943729111.729414</v>
+        <v>1670925079.360782</v>
       </c>
       <c r="G8" t="n">
-        <v>1913786390.729414</v>
+        <v>1640601973.360782</v>
       </c>
       <c r="H8" t="n">
-        <v>8438446</v>
+        <v>9242959</v>
       </c>
       <c r="I8" t="n">
-        <v>-75378353</v>
+        <v>-79310018</v>
       </c>
       <c r="J8" t="n">
-        <v>-74541706</v>
+        <v>-78516591</v>
       </c>
       <c r="K8" t="n">
-        <v>115832628</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16.78049738912436</v>
-      </c>
+        <v>-363833557</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>226.7937000164976</v>
+        <v>177.4974846648981</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3726803775274051</v>
+        <v>0.2971252117038761</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
@@ -1059,75 +1045,75 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2667870322.372668</v>
+        <v>-7100237321.594845</v>
       </c>
       <c r="S8" t="n">
-        <v>-1105748484.04561</v>
+        <v>-949522254.5256429</v>
       </c>
       <c r="T8" t="n">
-        <v>49674512.2782844</v>
+        <v>48647988.81388055</v>
       </c>
       <c r="U8" t="n">
-        <v>9466556637.252213</v>
+        <v>8975283068.536667</v>
       </c>
       <c r="V8" t="n">
-        <v>2769588246.964389</v>
+        <v>243542870.3075151</v>
       </c>
       <c r="W8" t="n">
-        <v>1.624367584385729</v>
+        <v>0.1428382519926514</v>
       </c>
       <c r="X8" t="n">
-        <v>-29.81884170472485</v>
+        <v>586.0907392817326</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SEKTÖR TOPLAM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>465809633109</v>
+        <v>488244967190</v>
       </c>
       <c r="C9" t="n">
         <v>9810898558</v>
       </c>
       <c r="D9" t="n">
-        <v>-182296870775</v>
+        <v>-148798955541</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>845476012983.876</v>
+        <v>779235009833.8927</v>
       </c>
       <c r="G9" t="n">
-        <v>663179142208.876</v>
+        <v>630436054292.8927</v>
       </c>
       <c r="H9" t="n">
-        <v>283613449024</v>
+        <v>317988096357</v>
       </c>
       <c r="I9" t="n">
-        <v>33873451527</v>
+        <v>39382725991</v>
       </c>
       <c r="J9" t="n">
-        <v>43528121398</v>
+        <v>50517859063</v>
       </c>
       <c r="K9" t="n">
-        <v>36708571505</v>
+        <v>39929911146</v>
       </c>
       <c r="L9" t="n">
-        <v>23.03211425344393</v>
+        <v>19.51506996809215</v>
       </c>
       <c r="M9" t="n">
-        <v>15.23564814904572</v>
+        <v>12.47946896377153</v>
       </c>
       <c r="N9" t="n">
-        <v>2.3383205009885</v>
+        <v>1.982577528893134</v>
       </c>
       <c r="O9" t="n">
-        <v>1.81506768621514</v>
+        <v>1.595991893820493</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0400643554717217</v>
+        <v>0.05054024202454033</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1143,53 +1129,53 @@
       <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>SEKTÖR Median</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17746392856</v>
+        <v>18936263841</v>
       </c>
       <c r="C10" t="n">
         <v>400000000</v>
       </c>
       <c r="D10" t="n">
-        <v>663098337</v>
+        <v>2319432829</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>36479998779.29688</v>
+        <v>41250645142.7002</v>
       </c>
       <c r="G10" t="n">
-        <v>53016161428.6499</v>
+        <v>57451770860.00586</v>
       </c>
       <c r="H10" t="n">
-        <v>16733157490</v>
+        <v>20338868404</v>
       </c>
       <c r="I10" t="n">
-        <v>231610000</v>
+        <v>466577034</v>
       </c>
       <c r="J10" t="n">
-        <v>290957000</v>
+        <v>526051573</v>
       </c>
       <c r="K10" t="n">
-        <v>1477665556</v>
+        <v>1754933090</v>
       </c>
       <c r="L10" t="n">
-        <v>16.78049738912436</v>
+        <v>14.60294171637756</v>
       </c>
       <c r="M10" t="n">
-        <v>12.57481920325784</v>
+        <v>9.969121272279752</v>
       </c>
       <c r="N10" t="n">
-        <v>2.727256665756355</v>
+        <v>2.22966606518622</v>
       </c>
       <c r="O10" t="n">
-        <v>1.715103134495471</v>
+        <v>1.471338375169714</v>
       </c>
       <c r="P10" t="n">
-        <v>4.44924412796512</v>
+        <v>5.766863245018089</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
